--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484882_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484882_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5392</v>
+        <v>6.0394</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7219</v>
+        <v>1.8504</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8172</v>
+        <v>4.1889</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3084</v>
+        <v>3.342</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5701</v>
+        <v>-0.126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7383</v>
+        <v>3.468</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5816</v>
+        <v>2.7754</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4497</v>
+        <v>0.2168</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1319</v>
+        <v>2.5586</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2732</v>
+        <v>0.5666</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8796</v>
+        <v>-0.3428</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.9094</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4531</v>
+        <v>0.3774</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4531</v>
+        <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4762</v>
+        <v>-0.2273</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1611</v>
+        <v>-0.2832</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6373</v>
+        <v>0.0559</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6985</v>
+        <v>2.5473</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6985</v>
+        <v>0.3018</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.2455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2062</v>
+        <v>5.616</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4406</v>
+        <v>2.8782</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7657</v>
+        <v>2.7379</v>
       </c>
       <c r="G3" t="n">
-        <v>3.342</v>
+        <v>3.3084</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.126</v>
+        <v>2.5701</v>
       </c>
       <c r="I3" t="n">
-        <v>3.468</v>
+        <v>0.7383</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7754</v>
+        <v>3.5816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2168</v>
+        <v>3.4497</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5586</v>
+        <v>0.1319</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5666</v>
+        <v>-0.2732</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3428</v>
+        <v>-0.8796</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9094</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0605</v>
+        <v>0.553</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6931</v>
+        <v>-0.0049</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3674</v>
+        <v>0.5579</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5473</v>
+        <v>-0.6985</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3018</v>
+        <v>-0.6985</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. LEMISHKA</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6247</v>
+        <v>0.9509</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.238</v>
+        <v>0.9509</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8627</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1089</v>
+        <v>0.9509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.9509</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5157</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7502</v>
+        <v>0.9509</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0238</v>
+        <v>0.9509</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2736</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6413</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3993</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6671</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5596</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1075</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>V. LEMISHKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9509</v>
+        <v>0.7056</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9509</v>
+        <v>-1.7638</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.4694</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9509</v>
+        <v>0.1089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9509</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.5157</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9509</v>
+        <v>0.7502</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9509</v>
+        <v>2.0238</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.2736</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.6413</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.3993</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.7579</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.748</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0337</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.7143</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3628</v>
+        <v>0.2543</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4966</v>
+        <v>-1.9512</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1338</v>
+        <v>2.2054</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7529</v>
+        <v>1.3865</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1033</v>
+        <v>-0.666</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6496</v>
+        <v>2.0525</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9188</v>
+        <v>0.5719</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2692</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6496</v>
+        <v>0.6666</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6717</v>
+        <v>0.8146</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3725</v>
+        <v>-0.5713</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2991</v>
+        <v>1.3859</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-4.7175</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>2.6418</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1157</v>
+        <v>-0.5846</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6343</v>
+        <v>-0.5788</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4814</v>
+        <v>-0.0058</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.528</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.7732</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9182</v>
+        <v>-0.2331</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5946</v>
+        <v>-2.3404</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6764</v>
+        <v>2.1073</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3865</v>
+        <v>0.7529</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.666</v>
+        <v>0.1033</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0525</v>
+        <v>0.6496</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5719</v>
+        <v>-0.9188</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.2692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6666</v>
+        <v>-0.6496</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8146</v>
+        <v>1.6717</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5713</v>
+        <v>0.3725</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3859</v>
+        <v>1.2991</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.7175</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6418</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7571</v>
+        <v>-0.986</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2222</v>
+        <v>-0.4781</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5349</v>
+        <v>-0.5078</v>
       </c>
       <c r="V8" t="n">
-        <v>1.528</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7732</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1758</v>
+        <v>-1.2497</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3692</v>
+        <v>-1.0689</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1934</v>
+        <v>-0.1808</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6903</v>
+        <v>0.396</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6192</v>
+        <v>0.7857</v>
       </c>
       <c r="I9" t="n">
-        <v>0.929</v>
+        <v>-0.3897</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1447</v>
+        <v>-0.2692</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5363</v>
+        <v>0.3803</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4545</v>
+        <v>0.6652</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0829</v>
+        <v>0.4054</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5374</v>
+        <v>0.2598</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4855</v>
+        <v>-0.3248</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3375</v>
+        <v>-0.1579</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.148</v>
+        <v>-0.1669</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5033</v>
+        <v>-1.7713</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3225</v>
+        <v>-4.7001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1808</v>
+        <v>2.9289</v>
       </c>
       <c r="G10" t="n">
-        <v>0.396</v>
+        <v>-0.6903</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7857</v>
+        <v>-1.6192</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3897</v>
+        <v>0.929</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2692</v>
+        <v>-2.1447</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3803</v>
+        <v>-1.5363</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6496</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6652</v>
+        <v>1.4545</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4054</v>
+        <v>-0.0829</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2598</v>
+        <v>1.5374</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5784</v>
+        <v>-1.081</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4115</v>
+        <v>-0.6684</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1669</v>
+        <v>-0.4126</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3817</v>
+        <v>-2.8727</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4596</v>
+        <v>-3.0828</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.2101</v>
       </c>
       <c r="G11" t="n">
         <v>0.198</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7036</v>
+        <v>0.2126</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9123</v>
+        <v>0.289</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2087</v>
+        <v>-0.0764</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6415999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0566</v>
+        <v>-2.9605</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2184</v>
+        <v>-4.4133</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1618</v>
+        <v>1.4528</v>
       </c>
       <c r="G12" t="n">
         <v>1.3788</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7372</v>
+        <v>-0.641</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0152</v>
+        <v>-0.1796</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7524</v>
+        <v>-0.4614</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2452</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.556500000000002</v>
+        <v>5.1128</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.9516</v>
+        <v>-13.0071</v>
       </c>
       <c r="F13" t="n">
-        <v>18.508</v>
+        <v>18.1199</v>
       </c>
       <c r="G13" t="n">
         <v>11.766</v>
@@ -1438,10 +1438,10 @@
         <v>3.9874</v>
       </c>
       <c r="I13" t="n">
-        <v>7.7787</v>
+        <v>7.778700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>5.609900000000001</v>
+        <v>5.609899999999999</v>
       </c>
       <c r="K13" t="n">
         <v>5.951599999999999</v>
@@ -1453,7 +1453,7 @@
         <v>6.156199999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.964299999999999</v>
+        <v>-1.9643</v>
       </c>
       <c r="O13" t="n">
         <v>8.1203</v>
@@ -1468,19 +1468,19 @@
         <v>14.9073</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8875000000000001</v>
+        <v>-1.3311</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9726</v>
+        <v>-2.0282</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0851</v>
+        <v>0.6971999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>2.4144</v>
       </c>
       <c r="W13" t="n">
-        <v>6.0551</v>
+        <v>6.055099999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-3.640700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3029</v>
+        <v>5.0696</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8774</v>
+        <v>2.4877</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4256</v>
+        <v>2.5819</v>
       </c>
       <c r="G14" t="n">
         <v>2.7363</v>
@@ -1546,13 +1546,13 @@
         <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0569</v>
+        <v>0.8236</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6183</v>
+        <v>0.2286</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4386</v>
+        <v>0.595</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9434</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7038</v>
+        <v>3.6551</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5406</v>
+        <v>-0.2389</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1633</v>
+        <v>3.894</v>
       </c>
       <c r="G15" t="n">
         <v>0.062</v>
@@ -1624,13 +1624,13 @@
         <v>3.5853</v>
       </c>
       <c r="S15" t="n">
-        <v>1.887</v>
+        <v>0.8383</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7388</v>
+        <v>-0.0407</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1482</v>
+        <v>0.8789</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7082</v>
+        <v>3.466</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1187</v>
+        <v>0.271</v>
       </c>
       <c r="F16" t="n">
-        <v>2.827</v>
+        <v>3.195</v>
       </c>
       <c r="G16" t="n">
         <v>0.4915</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5003</v>
+        <v>0.2575</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.458</v>
+        <v>-0.0682</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0423</v>
+        <v>0.3257</v>
       </c>
       <c r="V16" t="n">
         <v>2.5284</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1733</v>
+        <v>0.9593</v>
       </c>
       <c r="E17" t="n">
         <v>0.7009</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4724</v>
+        <v>0.2584</v>
       </c>
       <c r="G17" t="n">
         <v>1.276</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5009</v>
+        <v>0.2869</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1488</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6496</v>
+        <v>0.4356</v>
       </c>
       <c r="V17" t="n">
         <v>-1.547</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7857</v>
+        <v>-1.0025</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4383</v>
+        <v>-2.7563</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6526</v>
+        <v>1.7537</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1648</v>
@@ -1858,13 +1858,13 @@
         <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1305</v>
+        <v>0.6526</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7396</v>
+        <v>-0.0575</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6091</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2452</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2195</v>
+        <v>-1.6988</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9465</v>
+        <v>-0.8491</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.273</v>
+        <v>-0.8497</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5881</v>
@@ -1936,13 +1936,13 @@
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7637</v>
+        <v>-0.243</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3252</v>
+        <v>-0.2277</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4385</v>
+        <v>-0.0152</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9434</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3267</v>
+        <v>-2.3387</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.5447</v>
+        <v>-6.7396</v>
       </c>
       <c r="F20" t="n">
-        <v>4.218</v>
+        <v>4.4008</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0782</v>
@@ -2014,13 +2014,13 @@
         <v>3.3966</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0158</v>
+        <v>1.0037</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5596</v>
+        <v>0.3647</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4562</v>
+        <v>0.639</v>
       </c>
       <c r="V20" t="n">
         <v>0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6181</v>
+        <v>-2.8839</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2345</v>
+        <v>-2.5268</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3836</v>
+        <v>-0.3571</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5496</v>
@@ -2092,13 +2092,13 @@
         <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8559</v>
+        <v>0.59</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.3231</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2404</v>
+        <v>0.2669</v>
       </c>
       <c r="V21" t="n">
         <v>-1.547</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6984</v>
+        <v>-4.091</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8182</v>
+        <v>-4.5259</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1197</v>
+        <v>0.4348</v>
       </c>
       <c r="G22" t="n">
         <v>-5.8779</v>
@@ -2170,13 +2170,13 @@
         <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9717</v>
+        <v>-0.3643</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7984</v>
+        <v>-0.506</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1734</v>
+        <v>0.1417</v>
       </c>
       <c r="V22" t="n">
         <v>0.6415999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.3144</v>
+        <v>-6.9103</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6032</v>
+        <v>-6.4083</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7113</v>
+        <v>-0.502</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3498</v>
@@ -2248,13 +2248,13 @@
         <v>3.0192</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2287</v>
+        <v>0.1755</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3128</v>
+        <v>-0.1179</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.2934</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9054</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0746</v>
+        <v>-5.7752</v>
       </c>
       <c r="E24" t="n">
-        <v>-20.5852</v>
+        <v>-20.5853</v>
       </c>
       <c r="F24" t="n">
-        <v>13.5107</v>
+        <v>14.8098</v>
       </c>
       <c r="G24" t="n">
         <v>-13.0426</v>
@@ -2326,13 +2326,13 @@
         <v>22.644</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7216</v>
+        <v>4.020799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2507000000000002</v>
+        <v>-0.2504</v>
       </c>
       <c r="U24" t="n">
-        <v>2.972</v>
+        <v>4.2712</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4144</v>
